--- a/artfynd/A 53324-2021 artfynd.xlsx
+++ b/artfynd/A 53324-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53324-2021 artfynd.xlsx
+++ b/artfynd/A 53324-2021 artfynd.xlsx
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75624306</v>
+        <v>75631863</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lissmossen, intill NR, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629567.0744089446</v>
+        <v>629567</v>
       </c>
       <c r="R2" t="n">
-        <v>6688426.181149213</v>
+        <v>6688426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +752,14 @@
           <t>1999-06-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1999-06-15</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På undersidan av en böjd stamdel av levande gran, omkr. 72 cm.</t>
+          <t>1 ex. på levande asp, omkr. 106 cm.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,12 +773,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Undersidan av en böjd stamdel av levande gran. # Gran</t>
+          <t>Levande asp. # Asp</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75631863</v>
+        <v>75659899</v>
       </c>
       <c r="B3" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,9 +829,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>puppa</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>kokong</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629567.0744089446</v>
+        <v>629508</v>
       </c>
       <c r="R3" t="n">
-        <v>6688426.181149213</v>
+        <v>6688396</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,24 +883,14 @@
           <t>1999-06-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1999-06-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1 ex. på levande asp, omkr. 106 cm.</t>
+          <t>1 puppa i fnöskticka på björklåga, omkr. ca. 100 cm.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,12 +904,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Levande asp. # Asp</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 53324-2021 artfynd.xlsx
+++ b/artfynd/A 53324-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75631863</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,8 +934,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75659899</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>